--- a/research/traditional_assets/database/data/australia/australia_electronics_consumer_office.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_electronics_consumer_office.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,26 +587,23 @@
           <t>Electronics (Consumer &amp; Office)</t>
         </is>
       </c>
-      <c r="D2">
-        <v>0.187</v>
-      </c>
       <c r="G2">
-        <v>-0.05549146285186894</v>
+        <v>-1.88545362392296</v>
       </c>
       <c r="H2">
-        <v>-0.1742039686202123</v>
+        <v>-3.122149011657375</v>
       </c>
       <c r="I2">
-        <v>-0.2068912475003845</v>
+        <v>-3.208312214901166</v>
       </c>
       <c r="J2">
-        <v>-0.2068912475003845</v>
+        <v>-3.208312214901166</v>
       </c>
       <c r="K2">
-        <v>-10.79</v>
+        <v>-9.77</v>
       </c>
       <c r="L2">
-        <v>-0.207468081833564</v>
+        <v>-4.951849974657882</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +627,67 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>5.797000000000001</v>
+        <v>3.36</v>
       </c>
       <c r="V2">
-        <v>0.02669829134619814</v>
+        <v>0.02027149321266969</v>
       </c>
       <c r="W2">
-        <v>-0.4604966139954854</v>
+        <v>2.314515259355117</v>
       </c>
       <c r="X2">
-        <v>0.105005783728375</v>
+        <v>0.09068058715813394</v>
       </c>
       <c r="Y2">
-        <v>-0.5655023977238605</v>
+        <v>2.223834672196983</v>
       </c>
       <c r="Z2">
-        <v>2.657401256961831</v>
-      </c>
-      <c r="AA2">
-        <v>-11.43646408839779</v>
+        <v>1.93621197252208</v>
       </c>
       <c r="AB2">
-        <v>0.1034185134764919</v>
-      </c>
-      <c r="AC2">
-        <v>-11.53988260187428</v>
+        <v>0.08889317536268812</v>
       </c>
       <c r="AD2">
-        <v>15.529</v>
+        <v>3.09</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>15.529</v>
+        <v>3.09</v>
       </c>
       <c r="AG2">
-        <v>9.731999999999999</v>
+        <v>-0.27</v>
       </c>
       <c r="AH2">
-        <v>0.06674575236719835</v>
+        <v>0.01830135039090263</v>
       </c>
       <c r="AI2">
-        <v>0.2853598926845403</v>
+        <v>0.8512396694214878</v>
       </c>
       <c r="AJ2">
-        <v>0.04289832585448422</v>
+        <v>-0.001631617113850617</v>
       </c>
       <c r="AK2">
-        <v>0.2001563078441858</v>
+        <v>-1.000000000000001</v>
       </c>
       <c r="AL2">
-        <v>0.442</v>
+        <v>0.317</v>
       </c>
       <c r="AM2">
-        <v>0.44</v>
+        <v>0.307</v>
       </c>
       <c r="AN2">
-        <v>-1.702741228070175</v>
+        <v>-0.497584541062802</v>
       </c>
       <c r="AO2">
-        <v>-24.34389140271493</v>
+        <v>-19.96845425867508</v>
       </c>
       <c r="AP2">
-        <v>-1.067105263157895</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="AQ2">
-        <v>-24.45454545454545</v>
+        <v>-20.61889250814332</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +698,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Atomos Limited (ASX:AMS)</t>
+          <t>Audeara Limited (ASX:AUA)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -715,26 +706,23 @@
           <t>Electronics (Consumer &amp; Office)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.187</v>
-      </c>
       <c r="G3">
-        <v>0.01267326732673268</v>
+        <v>-1.357512953367876</v>
       </c>
       <c r="H3">
-        <v>-0.0594059405940594</v>
+        <v>-1.357512953367876</v>
       </c>
       <c r="I3">
-        <v>-0.0893069306930693</v>
+        <v>-1.378238341968912</v>
       </c>
       <c r="J3">
-        <v>-0.0893069306930693</v>
+        <v>-1.378238341968912</v>
       </c>
       <c r="K3">
-        <v>-7.14</v>
+        <v>-2.49</v>
       </c>
       <c r="L3">
-        <v>-0.1413861386138614</v>
+        <v>-1.290155440414508</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +746,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3.45</v>
+        <v>1.75</v>
       </c>
       <c r="V3">
-        <v>0.2875</v>
+        <v>0.6140350877192983</v>
       </c>
       <c r="W3">
-        <v>-0.1493723849372385</v>
+        <v>-0.8861209964412812</v>
       </c>
       <c r="X3">
-        <v>0.1517341514267184</v>
+        <v>0.0912307903889987</v>
       </c>
       <c r="Y3">
-        <v>-0.3011065363639569</v>
+        <v>-0.9773517868302799</v>
       </c>
       <c r="Z3">
-        <v>2.604435275915421</v>
+        <v>1.894013738959764</v>
       </c>
       <c r="AA3">
-        <v>-0.2325941206807633</v>
+        <v>-2.610402355250245</v>
       </c>
       <c r="AB3">
-        <v>0.09509861045205777</v>
+        <v>0.08862593398282484</v>
       </c>
       <c r="AC3">
-        <v>-0.327692731132821</v>
+        <v>-2.69902828923307</v>
       </c>
       <c r="AD3">
-        <v>12.6</v>
+        <v>0.14</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>12.6</v>
+        <v>0.14</v>
       </c>
       <c r="AG3">
-        <v>9.149999999999999</v>
+        <v>-1.61</v>
       </c>
       <c r="AH3">
-        <v>0.5121951219512195</v>
+        <v>0.04682274247491639</v>
       </c>
       <c r="AI3">
-        <v>0.252</v>
+        <v>0.06222222222222223</v>
       </c>
       <c r="AJ3">
-        <v>0.4326241134751773</v>
+        <v>-1.298387096774193</v>
       </c>
       <c r="AK3">
-        <v>0.19656283566058</v>
+        <v>-3.22</v>
       </c>
       <c r="AL3">
-        <v>0.363</v>
+        <v>0.008</v>
       </c>
       <c r="AM3">
-        <v>0.362</v>
+        <v>0.003</v>
       </c>
       <c r="AN3">
-        <v>-4.2</v>
+        <v>-0.0534351145038168</v>
       </c>
       <c r="AO3">
-        <v>-12.42424242424242</v>
+        <v>-332.5</v>
       </c>
       <c r="AP3">
-        <v>-3.049999999999999</v>
+        <v>0.6145038167938931</v>
       </c>
       <c r="AQ3">
-        <v>-12.4585635359116</v>
+        <v>-886.6666666666667</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Audeara Limited (ASX:AUA)</t>
+          <t>Audio Pixels Holdings Limited (ASX:AKP)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,22 +832,22 @@
         </is>
       </c>
       <c r="G4">
-        <v>-1.349295774647887</v>
+        <v>-25.58139534883721</v>
       </c>
       <c r="H4">
-        <v>-1.429577464788732</v>
+        <v>-82.32558139534885</v>
       </c>
       <c r="I4">
-        <v>-1.457746478873239</v>
+        <v>-85.34883720930233</v>
       </c>
       <c r="J4">
-        <v>-1.457746478873239</v>
+        <v>-85.34883720930233</v>
       </c>
       <c r="K4">
-        <v>-2.04</v>
+        <v>-7.28</v>
       </c>
       <c r="L4">
-        <v>-1.436619718309859</v>
+        <v>-169.3023255813954</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -883,189 +871,64 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1.98</v>
+        <v>1.61</v>
       </c>
       <c r="V4">
-        <v>0.2561448900388098</v>
+        <v>0.009883364027010436</v>
       </c>
       <c r="W4">
-        <v>-0.4604966139954854</v>
+        <v>5.515151515151515</v>
       </c>
       <c r="X4">
-        <v>0.105005783728375</v>
+        <v>0.09013038392726919</v>
       </c>
       <c r="Y4">
-        <v>-0.5655023977238605</v>
-      </c>
-      <c r="Z4">
-        <v>7.845303867403312</v>
-      </c>
-      <c r="AA4">
-        <v>-11.43646408839779</v>
+        <v>5.425021131224246</v>
       </c>
       <c r="AB4">
-        <v>0.1034185134764919</v>
-      </c>
-      <c r="AC4">
-        <v>-11.53988260187428</v>
+        <v>0.08916041674255139</v>
       </c>
       <c r="AD4">
-        <v>0.189</v>
+        <v>2.95</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.189</v>
+        <v>2.95</v>
       </c>
       <c r="AG4">
-        <v>-1.791</v>
+        <v>1.34</v>
       </c>
       <c r="AH4">
-        <v>0.02386664982952393</v>
+        <v>0.01778715706964124</v>
       </c>
       <c r="AI4">
-        <v>0.06302100700233411</v>
+        <v>2.13768115942029</v>
       </c>
       <c r="AJ4">
-        <v>-0.3015659201885839</v>
+        <v>0.008158792011690209</v>
       </c>
       <c r="AK4">
-        <v>-1.757605495583906</v>
+        <v>-5.82608695652174</v>
       </c>
       <c r="AL4">
-        <v>0.011</v>
+        <v>0.309</v>
       </c>
       <c r="AM4">
-        <v>0.011</v>
+        <v>0.304</v>
       </c>
       <c r="AN4">
-        <v>-0.09310344827586207</v>
+        <v>-0.8217270194986073</v>
       </c>
       <c r="AO4">
-        <v>-188.1818181818182</v>
+        <v>-11.87702265372168</v>
       </c>
       <c r="AP4">
-        <v>0.8822660098522168</v>
+        <v>-0.3732590529247911</v>
       </c>
       <c r="AQ4">
-        <v>-188.1818181818182</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Audio Pixels Holdings Limited (ASX:AKP)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Electronics (Consumer &amp; Office)</t>
-        </is>
-      </c>
-      <c r="G5">
-        <v>-18.29545454545455</v>
-      </c>
-      <c r="H5">
-        <v>-45.79545454545455</v>
-      </c>
-      <c r="I5">
-        <v>-47.5</v>
-      </c>
-      <c r="J5">
-        <v>-47.5</v>
-      </c>
-      <c r="K5">
-        <v>-1.61</v>
-      </c>
-      <c r="L5">
-        <v>-18.29545454545455</v>
-      </c>
-      <c r="M5">
-        <v>-0</v>
-      </c>
-      <c r="N5">
-        <v>-0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>-0</v>
-      </c>
-      <c r="Q5">
-        <v>-0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0.367</v>
-      </c>
-      <c r="V5">
-        <v>0.001859169199594732</v>
-      </c>
-      <c r="W5">
-        <v>-0.6598360655737705</v>
-      </c>
-      <c r="X5">
-        <v>0.1045241814892468</v>
-      </c>
-      <c r="Y5">
-        <v>-0.7643602470630173</v>
-      </c>
-      <c r="AB5">
-        <v>0.1036202829318343</v>
-      </c>
-      <c r="AD5">
-        <v>2.74</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>2.74</v>
-      </c>
-      <c r="AG5">
-        <v>2.373</v>
-      </c>
-      <c r="AH5">
-        <v>0.01369041670830419</v>
-      </c>
-      <c r="AI5">
-        <v>1.929577464788732</v>
-      </c>
-      <c r="AJ5">
-        <v>0.01187848207715757</v>
-      </c>
-      <c r="AK5">
-        <v>2.253561253561253</v>
-      </c>
-      <c r="AL5">
-        <v>0.068</v>
-      </c>
-      <c r="AM5">
-        <v>0.067</v>
-      </c>
-      <c r="AN5">
-        <v>-0.6699266503667483</v>
-      </c>
-      <c r="AO5">
-        <v>-61.47058823529411</v>
-      </c>
-      <c r="AP5">
-        <v>-0.580195599022005</v>
-      </c>
-      <c r="AQ5">
-        <v>-62.38805970149253</v>
+        <v>-12.07236842105263</v>
       </c>
     </row>
   </sheetData>
